--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98770</v>
+        <v>98773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98773</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98779</v>
+        <v>98781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
